--- a/backend/excel/Conveyor Calculation.xlsx
+++ b/backend/excel/Conveyor Calculation.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BIT\Desktop\SAIL\Conveyor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BIT\Desktop\SAIL\mechanical-calculator\backend\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353ACB14-6037-4358-9801-695BDEAEC1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D650510B-B2A3-485A-A851-4D064D6FF296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Belt Conveyor Motor Power Calcu" sheetId="1" r:id="rId1"/>
+    <sheet name="Belt Conveyor Motor Power" sheetId="1" r:id="rId1"/>
     <sheet name="Density - IS8730" sheetId="2" r:id="rId2"/>
     <sheet name="Table 7 - Max Area" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -2720,7 +2720,7 @@
       <c r="E8" s="15"/>
     </row>
     <row r="9" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="20" t="s">
         <v>629</v>
       </c>
       <c r="C9" s="27"/>
@@ -4670,7 +4670,7 @@
     <mergeCell ref="J116:K116"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="2">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{694FE722-088F-4312-925E-5C2F1206CF40}">
       <formula1>$F$118:$F$121</formula1>
     </dataValidation>
@@ -4681,7 +4681,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="4">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C0683956-953A-4630-ACA1-744E176AFD82}">
           <x14:formula1>
             <xm:f>'Table 7 - Max Area'!$A$3:$A$54</xm:f>
@@ -8421,7 +8421,7 @@
         <v>559</v>
       </c>
       <c r="K2" s="45">
-        <f>'Belt Conveyor Motor Power Calcu'!D13</f>
+        <f>'Belt Conveyor Motor Power'!D13</f>
         <v>800</v>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
         <v>615</v>
       </c>
       <c r="K3" s="45">
-        <f>'Belt Conveyor Motor Power Calcu'!D14</f>
+        <f>'Belt Conveyor Motor Power'!D14</f>
         <v>25</v>
       </c>
     </row>
@@ -8487,7 +8487,7 @@
         <v>616</v>
       </c>
       <c r="K4" s="45">
-        <f>'Belt Conveyor Motor Power Calcu'!D15</f>
+        <f>'Belt Conveyor Motor Power'!D15</f>
         <v>30</v>
       </c>
     </row>
